--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/153.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/153.xlsx
@@ -426,13 +426,13 @@
         <v>-11.68299183839152</v>
       </c>
       <c r="E2">
-        <v>-23.14600721684003</v>
+        <v>-20.17020638333243</v>
       </c>
       <c r="F2">
-        <v>-0.5670101791571441</v>
+        <v>-1.671717634060954</v>
       </c>
       <c r="G2">
-        <v>-13.37070074443818</v>
+        <v>-11.55902936107153</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.44895336188183</v>
       </c>
       <c r="E3">
-        <v>-24.34170845083552</v>
+        <v>-20.66298906023466</v>
       </c>
       <c r="F3">
-        <v>0.4077446543302845</v>
+        <v>-1.328059476600745</v>
       </c>
       <c r="G3">
-        <v>-12.75534171745131</v>
+        <v>-11.65743485157207</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.18567545366169</v>
       </c>
       <c r="E4">
-        <v>-23.4409599787067</v>
+        <v>-20.24136750617204</v>
       </c>
       <c r="F4">
-        <v>-0.07138305144894955</v>
+        <v>-1.444908982439643</v>
       </c>
       <c r="G4">
-        <v>-12.31081676278392</v>
+        <v>-10.89624354784249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.92058602573487</v>
       </c>
       <c r="E5">
-        <v>-25.06999482270082</v>
+        <v>-21.89998152122159</v>
       </c>
       <c r="F5">
-        <v>0.3590200836976176</v>
+        <v>-1.665383936899149</v>
       </c>
       <c r="G5">
-        <v>-12.18001715339685</v>
+        <v>-10.91726134717325</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.66254569055894</v>
       </c>
       <c r="E6">
-        <v>-22.74762703335115</v>
+        <v>-21.62372236352797</v>
       </c>
       <c r="F6">
-        <v>0.7196879374069112</v>
+        <v>-1.474693760774702</v>
       </c>
       <c r="G6">
-        <v>-12.07273643665883</v>
+        <v>-11.09253237992534</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.42863604113656</v>
       </c>
       <c r="E7">
-        <v>-25.40110959557278</v>
+        <v>-22.43313756541248</v>
       </c>
       <c r="F7">
-        <v>0.3292237082189194</v>
+        <v>-1.634365719501321</v>
       </c>
       <c r="G7">
-        <v>-11.76807429122657</v>
+        <v>-11.08573139026549</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.22286865711546</v>
       </c>
       <c r="E8">
-        <v>-27.06278037415741</v>
+        <v>-22.92707898827434</v>
       </c>
       <c r="F8">
-        <v>0.1226520722480011</v>
+        <v>-1.398015103767163</v>
       </c>
       <c r="G8">
-        <v>-12.56020552910543</v>
+        <v>-10.63721069100141</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.05690424956205</v>
       </c>
       <c r="E9">
-        <v>-25.67294973641678</v>
+        <v>-23.42869554566448</v>
       </c>
       <c r="F9">
-        <v>-0.07709712979346053</v>
+        <v>-1.157983223294965</v>
       </c>
       <c r="G9">
-        <v>-11.13961715862607</v>
+        <v>-10.03376710232837</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.928732824082784</v>
       </c>
       <c r="E10">
-        <v>-25.93372156908012</v>
+        <v>-23.81010986089144</v>
       </c>
       <c r="F10">
-        <v>-0.0932552643524677</v>
+        <v>-1.22222725721908</v>
       </c>
       <c r="G10">
-        <v>-11.03081568316372</v>
+        <v>-9.870395843422573</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.847019034707195</v>
       </c>
       <c r="E11">
-        <v>-26.72402784565909</v>
+        <v>-25.30616303147588</v>
       </c>
       <c r="F11">
-        <v>0.4859856122595034</v>
+        <v>-1.109180786126435</v>
       </c>
       <c r="G11">
-        <v>-10.91522888250907</v>
+        <v>-9.719612289562825</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.812400113729936</v>
       </c>
       <c r="E12">
-        <v>-27.34496616441156</v>
+        <v>-25.04560301259011</v>
       </c>
       <c r="F12">
-        <v>0.2430801252669932</v>
+        <v>-0.87354422309349</v>
       </c>
       <c r="G12">
-        <v>-10.03211711174679</v>
+        <v>-9.11993992145165</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.827911271820257</v>
       </c>
       <c r="E13">
-        <v>-28.39873970780368</v>
+        <v>-25.83490421202847</v>
       </c>
       <c r="F13">
-        <v>0.958463184529063</v>
+        <v>-1.013047920664149</v>
       </c>
       <c r="G13">
-        <v>-9.931399806910822</v>
+        <v>-9.277863861768092</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.897908983067207</v>
       </c>
       <c r="E14">
-        <v>-28.17052697532134</v>
+        <v>-25.66471807157097</v>
       </c>
       <c r="F14">
-        <v>0.780675659070622</v>
+        <v>-0.8539607893239068</v>
       </c>
       <c r="G14">
-        <v>-10.78964031932585</v>
+        <v>-8.348167269894287</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.01618345684037</v>
       </c>
       <c r="E15">
-        <v>-28.38020807887229</v>
+        <v>-27.23932508115322</v>
       </c>
       <c r="F15">
-        <v>0.9368610193988575</v>
+        <v>-0.5067340250924381</v>
       </c>
       <c r="G15">
-        <v>-10.23359871482137</v>
+        <v>-8.351206176598343</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.17844955511229</v>
       </c>
       <c r="E16">
-        <v>-32.32797457570121</v>
+        <v>-27.36778806064149</v>
       </c>
       <c r="F16">
-        <v>1.411296852208635</v>
+        <v>-0.4513079621711232</v>
       </c>
       <c r="G16">
-        <v>-9.601307703788821</v>
+        <v>-8.471908731279283</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.36516851238994</v>
       </c>
       <c r="E17">
-        <v>-29.77406317838668</v>
+        <v>-27.97338441676004</v>
       </c>
       <c r="F17">
-        <v>1.096654748133688</v>
+        <v>-0.193644281530337</v>
       </c>
       <c r="G17">
-        <v>-8.823281013563447</v>
+        <v>-7.998553324092238</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.56120457660105</v>
       </c>
       <c r="E18">
-        <v>-31.36706683753225</v>
+        <v>-28.50573058474259</v>
       </c>
       <c r="F18">
-        <v>1.736921451309899</v>
+        <v>-0.01495052213323323</v>
       </c>
       <c r="G18">
-        <v>-9.414772613498368</v>
+        <v>-7.764763756702634</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.74264006407646</v>
       </c>
       <c r="E19">
-        <v>-32.26130099769806</v>
+        <v>-29.47258987474002</v>
       </c>
       <c r="F19">
-        <v>1.634828482384471</v>
+        <v>-0.07068556609579237</v>
       </c>
       <c r="G19">
-        <v>-8.657872068504282</v>
+        <v>-7.350899386513287</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.88923234270124</v>
       </c>
       <c r="E20">
-        <v>-33.23376504637836</v>
+        <v>-29.51658899551525</v>
       </c>
       <c r="F20">
-        <v>2.285163162974306</v>
+        <v>0.2757940107383512</v>
       </c>
       <c r="G20">
-        <v>-8.957513752087833</v>
+        <v>-7.022036944093702</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.98715180971215</v>
       </c>
       <c r="E21">
-        <v>-32.77685157908301</v>
+        <v>-30.61709031952302</v>
       </c>
       <c r="F21">
-        <v>1.683259810956546</v>
+        <v>0.4645126724441346</v>
       </c>
       <c r="G21">
-        <v>-7.909724044751903</v>
+        <v>-7.545256267598716</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.02218276021134</v>
       </c>
       <c r="E22">
-        <v>-33.12254412370511</v>
+        <v>-30.65790808042344</v>
       </c>
       <c r="F22">
-        <v>2.992385146583996</v>
+        <v>0.5949904787938903</v>
       </c>
       <c r="G22">
-        <v>-8.779524934216388</v>
+        <v>-7.105753080152341</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.99421015885767</v>
       </c>
       <c r="E23">
-        <v>-34.1334399133797</v>
+        <v>-31.0730796972986</v>
       </c>
       <c r="F23">
-        <v>2.963289569928066</v>
+        <v>1.018173563657657</v>
       </c>
       <c r="G23">
-        <v>-8.568700781622512</v>
+        <v>-7.06072556818941</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.90116648819487</v>
       </c>
       <c r="E24">
-        <v>-33.87862170915052</v>
+        <v>-31.31239811686353</v>
       </c>
       <c r="F24">
-        <v>3.24188443810279</v>
+        <v>0.9761123804131093</v>
       </c>
       <c r="G24">
-        <v>-8.451674155325859</v>
+        <v>-6.996198404875454</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.75286561991137</v>
       </c>
       <c r="E25">
-        <v>-36.02268798311398</v>
+        <v>-31.74673265079145</v>
       </c>
       <c r="F25">
-        <v>3.249304953297068</v>
+        <v>1.070561174945503</v>
       </c>
       <c r="G25">
-        <v>-8.440938773567202</v>
+        <v>-7.245527124071364</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.55814305721535</v>
       </c>
       <c r="E26">
-        <v>-34.29393661181638</v>
+        <v>-31.8372788874897</v>
       </c>
       <c r="F26">
-        <v>2.867831823899062</v>
+        <v>0.981897698354261</v>
       </c>
       <c r="G26">
-        <v>-9.346651760254746</v>
+        <v>-7.043828829195725</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.3270333361989</v>
       </c>
       <c r="E27">
-        <v>-34.86261507246853</v>
+        <v>-31.64458441825729</v>
       </c>
       <c r="F27">
-        <v>2.292881890433592</v>
+        <v>1.044853620967023</v>
       </c>
       <c r="G27">
-        <v>-9.422350299674076</v>
+        <v>-6.746903625359228</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.07561663153972</v>
       </c>
       <c r="E28">
-        <v>-34.40895149303486</v>
+        <v>-31.2627630883205</v>
       </c>
       <c r="F28">
-        <v>2.999429582977402</v>
+        <v>1.017537377492307</v>
       </c>
       <c r="G28">
-        <v>-8.255472783186809</v>
+        <v>-7.164586209513079</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.810380540973355</v>
       </c>
       <c r="E29">
-        <v>-34.60660281998344</v>
+        <v>-32.10630938087245</v>
       </c>
       <c r="F29">
-        <v>2.836491371581545</v>
+        <v>0.964177262873574</v>
       </c>
       <c r="G29">
-        <v>-9.051705500818313</v>
+        <v>-7.510846653887842</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.543959052192967</v>
       </c>
       <c r="E30">
-        <v>-34.11989629124944</v>
+        <v>-31.75846962599541</v>
       </c>
       <c r="F30">
-        <v>2.494912416302363</v>
+        <v>1.006843154322165</v>
       </c>
       <c r="G30">
-        <v>-9.219276142398918</v>
+        <v>-7.416105343420933</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.277949669762297</v>
       </c>
       <c r="E31">
-        <v>-34.73858979928084</v>
+        <v>-31.51224856920862</v>
       </c>
       <c r="F31">
-        <v>2.602409654163655</v>
+        <v>1.090287916275771</v>
       </c>
       <c r="G31">
-        <v>-9.888417813335028</v>
+        <v>-7.585592271531416</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.013749902699935</v>
       </c>
       <c r="E32">
-        <v>-31.44867536345946</v>
+        <v>-31.17087536436433</v>
       </c>
       <c r="F32">
-        <v>2.71353845471882</v>
+        <v>1.116568700496988</v>
       </c>
       <c r="G32">
-        <v>-8.992267984084732</v>
+        <v>-7.518762431488098</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.749788896942583</v>
       </c>
       <c r="E33">
-        <v>-34.40483150740063</v>
+        <v>-31.31948764859501</v>
       </c>
       <c r="F33">
-        <v>2.886367372904104</v>
+        <v>0.8471587700845047</v>
       </c>
       <c r="G33">
-        <v>-9.805574971342116</v>
+        <v>-7.247025691466662</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.477298616209856</v>
       </c>
       <c r="E34">
-        <v>-33.99843977926616</v>
+        <v>-30.95788415138749</v>
       </c>
       <c r="F34">
-        <v>2.83754008471349</v>
+        <v>0.9516589746824679</v>
       </c>
       <c r="G34">
-        <v>-8.712020216696267</v>
+        <v>-7.422527775115071</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.196947294375873</v>
       </c>
       <c r="E35">
-        <v>-33.72285967162414</v>
+        <v>-29.53588689193607</v>
       </c>
       <c r="F35">
-        <v>2.666777114830788</v>
+        <v>0.9797108084108703</v>
       </c>
       <c r="G35">
-        <v>-8.750840683393827</v>
+        <v>-7.436672789309723</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.900191525405397</v>
       </c>
       <c r="E36">
-        <v>-33.03893790313065</v>
+        <v>-29.21490803130236</v>
       </c>
       <c r="F36">
-        <v>2.683246715533248</v>
+        <v>0.7765155979737628</v>
       </c>
       <c r="G36">
-        <v>-8.295042533582018</v>
+        <v>-7.450569782768219</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.59036596013943</v>
       </c>
       <c r="E37">
-        <v>-31.49183345894142</v>
+        <v>-29.95760604646482</v>
       </c>
       <c r="F37">
-        <v>2.494463441170046</v>
+        <v>0.6321071370111278</v>
       </c>
       <c r="G37">
-        <v>-8.529942972795141</v>
+        <v>-7.377949311221812</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.268164826417192</v>
       </c>
       <c r="E38">
-        <v>-31.87177961396505</v>
+        <v>-29.1606837042454</v>
       </c>
       <c r="F38">
-        <v>2.690027731092565</v>
+        <v>0.7290998478375191</v>
       </c>
       <c r="G38">
-        <v>-8.492935668216109</v>
+        <v>-7.283915512539093</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.938190727780994</v>
       </c>
       <c r="E39">
-        <v>-32.63668485008137</v>
+        <v>-28.72611451387763</v>
       </c>
       <c r="F39">
-        <v>2.493780866430139</v>
+        <v>0.6680417149445703</v>
       </c>
       <c r="G39">
-        <v>-8.52235484364107</v>
+        <v>-6.685321381944048</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.609430499514343</v>
       </c>
       <c r="E40">
-        <v>-30.5237635078428</v>
+        <v>-28.17694784002952</v>
       </c>
       <c r="F40">
-        <v>2.007355243832242</v>
+        <v>0.6422281299385322</v>
       </c>
       <c r="G40">
-        <v>-8.825531475400986</v>
+        <v>-7.119738838926935</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.286784708114381</v>
       </c>
       <c r="E41">
-        <v>-31.83261690777758</v>
+        <v>-27.8465827218017</v>
       </c>
       <c r="F41">
-        <v>3.081245774617104</v>
+        <v>0.611357361938403</v>
       </c>
       <c r="G41">
-        <v>-8.365270257710669</v>
+        <v>-7.269162194854712</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.984320433554373</v>
       </c>
       <c r="E42">
-        <v>-30.98689433249142</v>
+        <v>-27.16702182519928</v>
       </c>
       <c r="F42">
-        <v>2.477949108627835</v>
+        <v>0.6945080534640146</v>
       </c>
       <c r="G42">
-        <v>-8.081918315003371</v>
+        <v>-6.753425265347829</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.707805385043296</v>
       </c>
       <c r="E43">
-        <v>-31.77374306064247</v>
+        <v>-26.42348070813787</v>
       </c>
       <c r="F43">
-        <v>2.437932336133397</v>
+        <v>1.01088061704341</v>
       </c>
       <c r="G43">
-        <v>-8.429298768807723</v>
+        <v>-7.146519856942574</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.469347705273966</v>
       </c>
       <c r="E44">
-        <v>-31.81407697242354</v>
+        <v>-27.06206186859821</v>
       </c>
       <c r="F44">
-        <v>2.008909261079894</v>
+        <v>0.6978985612436729</v>
       </c>
       <c r="G44">
-        <v>-7.509311536068268</v>
+        <v>-6.877743701287462</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.274132373334119</v>
       </c>
       <c r="E45">
-        <v>-29.7824651248968</v>
+        <v>-26.55144945547849</v>
       </c>
       <c r="F45">
-        <v>1.969820260076591</v>
+        <v>0.742734775287599</v>
       </c>
       <c r="G45">
-        <v>-8.027293705923508</v>
+        <v>-6.624261287447091</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.126179835409188</v>
       </c>
       <c r="E46">
-        <v>-30.16285982674351</v>
+        <v>-26.3403334174148</v>
       </c>
       <c r="F46">
-        <v>2.613055832024435</v>
+        <v>0.4378276449303514</v>
       </c>
       <c r="G46">
-        <v>-8.006829384446068</v>
+        <v>-6.680353134987159</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.02790251727065</v>
       </c>
       <c r="E47">
-        <v>-28.73537202192067</v>
+        <v>-24.95810730960994</v>
       </c>
       <c r="F47">
-        <v>2.241837891073087</v>
+        <v>0.7676620071726417</v>
       </c>
       <c r="G47">
-        <v>-7.412317153019227</v>
+        <v>-6.525441993928862</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.975947350209844</v>
       </c>
       <c r="E48">
-        <v>-28.64648291654103</v>
+        <v>-25.05623938679299</v>
       </c>
       <c r="F48">
-        <v>2.082203208879594</v>
+        <v>0.615080045046584</v>
       </c>
       <c r="G48">
-        <v>-7.590061866271402</v>
+        <v>-6.387176960383502</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.969071061768556</v>
       </c>
       <c r="E49">
-        <v>-29.79015479566472</v>
+        <v>-24.95723513523173</v>
       </c>
       <c r="F49">
-        <v>2.666263527041052</v>
+        <v>0.8990758686875608</v>
       </c>
       <c r="G49">
-        <v>-7.137617217886878</v>
+        <v>-6.846070147908075</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.997938538908393</v>
       </c>
       <c r="E50">
-        <v>-28.1437325324592</v>
+        <v>-24.59963118053002</v>
       </c>
       <c r="F50">
-        <v>2.294616491775054</v>
+        <v>0.5584155728580837</v>
       </c>
       <c r="G50">
-        <v>-7.552493251605282</v>
+        <v>-6.945189677054283</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.058154965566612</v>
       </c>
       <c r="E51">
-        <v>-27.79727164374201</v>
+        <v>-23.67185776231054</v>
       </c>
       <c r="F51">
-        <v>2.53492256185758</v>
+        <v>0.3484683397207575</v>
       </c>
       <c r="G51">
-        <v>-7.242937265436979</v>
+        <v>-7.165873306596497</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.140411185547624</v>
       </c>
       <c r="E52">
-        <v>-28.2513484677025</v>
+        <v>-24.18085042301358</v>
       </c>
       <c r="F52">
-        <v>2.494238125236485</v>
+        <v>0.6164567916700368</v>
       </c>
       <c r="G52">
-        <v>-8.267572278994324</v>
+        <v>-6.947343541341951</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.238400791242039</v>
       </c>
       <c r="E53">
-        <v>-25.16775726407596</v>
+        <v>-23.01478650503207</v>
       </c>
       <c r="F53">
-        <v>2.687612211746001</v>
+        <v>0.4331871307398685</v>
       </c>
       <c r="G53">
-        <v>-7.956217489802745</v>
+        <v>-6.874965869042517</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.3453145444626</v>
       </c>
       <c r="E54">
-        <v>-26.92223154971388</v>
+        <v>-22.72151994696328</v>
       </c>
       <c r="F54">
-        <v>1.964914668317212</v>
+        <v>0.5720480152059553</v>
       </c>
       <c r="G54">
-        <v>-7.525174420203872</v>
+        <v>-6.952729507433418</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.45473330469608</v>
       </c>
       <c r="E55">
-        <v>-26.03498101439076</v>
+        <v>-22.57918524165008</v>
       </c>
       <c r="F55">
-        <v>1.759310565472763</v>
+        <v>0.5433633087818139</v>
       </c>
       <c r="G55">
-        <v>-7.780977785985743</v>
+        <v>-6.940764464972346</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.563641263629017</v>
       </c>
       <c r="E56">
-        <v>-26.34025450639963</v>
+        <v>-22.46037432528071</v>
       </c>
       <c r="F56">
-        <v>2.071507328974647</v>
+        <v>0.2546159697183791</v>
       </c>
       <c r="G56">
-        <v>-7.318481770925433</v>
+        <v>-7.419742110636354</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.66597084442561</v>
       </c>
       <c r="E57">
-        <v>-26.53950066649696</v>
+        <v>-21.33639905086501</v>
       </c>
       <c r="F57">
-        <v>1.65335740445029</v>
+        <v>0.4078473718882316</v>
       </c>
       <c r="G57">
-        <v>-8.111749988073727</v>
+        <v>-7.461887360570695</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.761902634262276</v>
       </c>
       <c r="E58">
-        <v>-25.61660727158416</v>
+        <v>-21.91240792950548</v>
       </c>
       <c r="F58">
-        <v>1.872584837601179</v>
+        <v>0.4651737096315686</v>
       </c>
       <c r="G58">
-        <v>-8.091123800431637</v>
+        <v>-7.166447670406543</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.847632851768393</v>
       </c>
       <c r="E59">
-        <v>-26.57327873420179</v>
+        <v>-21.99943431960594</v>
       </c>
       <c r="F59">
-        <v>1.813386389527515</v>
+        <v>0.3804839114715556</v>
       </c>
       <c r="G59">
-        <v>-8.348588905145752</v>
+        <v>-7.678704477373471</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.923515281984132</v>
       </c>
       <c r="E60">
-        <v>-23.48633796564178</v>
+        <v>-21.50090359823014</v>
       </c>
       <c r="F60">
-        <v>2.604430870626486</v>
+        <v>0.3832945620692543</v>
       </c>
       <c r="G60">
-        <v>-7.909678356721559</v>
+        <v>-7.291685088442247</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.989439448571686</v>
       </c>
       <c r="E61">
-        <v>-24.50983875168722</v>
+        <v>-21.79981437048938</v>
       </c>
       <c r="F61">
-        <v>2.321937705454188</v>
+        <v>0.3175884596791975</v>
       </c>
       <c r="G61">
-        <v>-7.549310753948714</v>
+        <v>-7.610866889917983</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.044558798243957</v>
       </c>
       <c r="E62">
-        <v>-26.5894388794667</v>
+        <v>-20.78401363824016</v>
       </c>
       <c r="F62">
-        <v>1.553217725860663</v>
+        <v>0.2016137098176555</v>
       </c>
       <c r="G62">
-        <v>-9.288275511197451</v>
+        <v>-8.071960935132866</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.089986528712936</v>
       </c>
       <c r="E63">
-        <v>-24.64315683521422</v>
+        <v>-20.23630058835575</v>
       </c>
       <c r="F63">
-        <v>1.619362862974204</v>
+        <v>0.3147736672444848</v>
       </c>
       <c r="G63">
-        <v>-8.440363104384861</v>
+        <v>-7.991014799085398</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.122286591843952</v>
       </c>
       <c r="E64">
-        <v>-24.34430420791353</v>
+        <v>-21.36730724954438</v>
       </c>
       <c r="F64">
-        <v>2.60918404278375</v>
+        <v>0.4075085696204866</v>
       </c>
       <c r="G64">
-        <v>-9.433581722905044</v>
+        <v>-8.21647609122935</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.142929875870742</v>
       </c>
       <c r="E65">
-        <v>-24.42787097298041</v>
+        <v>-20.95876000473233</v>
       </c>
       <c r="F65">
-        <v>2.088864939532908</v>
+        <v>-0.02178455320632915</v>
       </c>
       <c r="G65">
-        <v>-8.564028854176716</v>
+        <v>-8.248904149795569</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.148964625938782</v>
       </c>
       <c r="E66">
-        <v>-23.82465856016231</v>
+        <v>-20.99126718977176</v>
       </c>
       <c r="F66">
-        <v>1.703203584546347</v>
+        <v>-0.06366183888745536</v>
       </c>
       <c r="G66">
-        <v>-7.708892517080514</v>
+        <v>-8.29846130362408</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.139556274296951</v>
       </c>
       <c r="E67">
-        <v>-25.03860485150777</v>
+        <v>-20.3168188963102</v>
       </c>
       <c r="F67">
-        <v>2.137387388519291</v>
+        <v>0.0744634553249454</v>
       </c>
       <c r="G67">
-        <v>-9.871239113925501</v>
+        <v>-8.46845471618524</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.116340270326931</v>
       </c>
       <c r="E68">
-        <v>-22.56543811216489</v>
+        <v>-20.33476492244478</v>
       </c>
       <c r="F68">
-        <v>1.096028502377171</v>
+        <v>0.126482443118546</v>
       </c>
       <c r="G68">
-        <v>-9.00709570798996</v>
+        <v>-8.138430492422609</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.078706376637316</v>
       </c>
       <c r="E69">
-        <v>-22.07629780159454</v>
+        <v>-20.37620566504392</v>
       </c>
       <c r="F69">
-        <v>2.110364387105166</v>
+        <v>-0.2782702954003345</v>
       </c>
       <c r="G69">
-        <v>-9.673154089563964</v>
+        <v>-8.500158293127424</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.030373140378511</v>
       </c>
       <c r="E70">
-        <v>-23.97051518867896</v>
+        <v>-20.65823778647906</v>
       </c>
       <c r="F70">
-        <v>1.66418416640488</v>
+        <v>-0.1267171655885537</v>
       </c>
       <c r="G70">
-        <v>-9.093186316254217</v>
+        <v>-7.677913421762364</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.969625940898575</v>
       </c>
       <c r="E71">
-        <v>-25.70178548264507</v>
+        <v>-20.57913157037505</v>
       </c>
       <c r="F71">
-        <v>1.542445636154659</v>
+        <v>-0.2852310666860587</v>
       </c>
       <c r="G71">
-        <v>-8.314197566647016</v>
+        <v>-8.29773290588316</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.898338321675959</v>
       </c>
       <c r="E72">
-        <v>-24.81412793261211</v>
+        <v>-20.3094760186879</v>
       </c>
       <c r="F72">
-        <v>0.905561985451481</v>
+        <v>-0.3493384199887125</v>
       </c>
       <c r="G72">
-        <v>-8.732797827524642</v>
+        <v>-8.202656114736293</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.815910728678147</v>
       </c>
       <c r="E73">
-        <v>-26.55980571666404</v>
+        <v>-20.89461365582035</v>
       </c>
       <c r="F73">
-        <v>1.000820923303813</v>
+        <v>-0.3222922242873086</v>
       </c>
       <c r="G73">
-        <v>-7.560239330807115</v>
+        <v>-8.218871449391697</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.719840388448491</v>
       </c>
       <c r="E74">
-        <v>-24.06205611948951</v>
+        <v>-21.09487735269225</v>
       </c>
       <c r="F74">
-        <v>0.8501839678395284</v>
+        <v>-0.4648650230853399</v>
       </c>
       <c r="G74">
-        <v>-8.882091951595161</v>
+        <v>-8.490737421270392</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.610844247676889</v>
       </c>
       <c r="E75">
-        <v>-23.63967037454312</v>
+        <v>-21.10322115424384</v>
       </c>
       <c r="F75">
-        <v>1.289659382781556</v>
+        <v>-0.6400672138796437</v>
       </c>
       <c r="G75">
-        <v>-8.451252520074394</v>
+        <v>-7.925015175822054</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.483802440751286</v>
       </c>
       <c r="E76">
-        <v>-26.28304402040012</v>
+        <v>-21.02487497581227</v>
       </c>
       <c r="F76">
-        <v>0.7269991081040196</v>
+        <v>-0.481192972961921</v>
       </c>
       <c r="G76">
-        <v>-9.311821816664702</v>
+        <v>-7.655508011681429</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.339579141459565</v>
       </c>
       <c r="E77">
-        <v>-23.26035758424653</v>
+        <v>-21.61672004923431</v>
       </c>
       <c r="F77">
-        <v>0.7390568240191692</v>
+        <v>-0.6795737120539578</v>
       </c>
       <c r="G77">
-        <v>-8.777686970024245</v>
+        <v>-7.447742346376043</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.175914955931655</v>
       </c>
       <c r="E78">
-        <v>-25.6336769701292</v>
+        <v>-22.27180607149952</v>
       </c>
       <c r="F78">
-        <v>0.9598879764618782</v>
+        <v>-0.7746694615279383</v>
       </c>
       <c r="G78">
-        <v>-8.816190231253984</v>
+        <v>-7.417794495171383</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.993321487535166</v>
       </c>
       <c r="E79">
-        <v>-25.27459031898453</v>
+        <v>-22.71401924731064</v>
       </c>
       <c r="F79">
-        <v>0.7866167100835</v>
+        <v>-0.8540320289205476</v>
       </c>
       <c r="G79">
-        <v>-7.757629897107417</v>
+        <v>-7.34806933937652</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.793682123792355</v>
       </c>
       <c r="E80">
-        <v>-26.06834376096311</v>
+        <v>-22.20112256796226</v>
       </c>
       <c r="F80">
-        <v>0.6518504456894512</v>
+        <v>-0.9291815197025188</v>
       </c>
       <c r="G80">
-        <v>-7.695384524566094</v>
+        <v>-7.043267519108635</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.576464883152917</v>
       </c>
       <c r="E81">
-        <v>-25.81766423181911</v>
+        <v>-23.23058321225884</v>
       </c>
       <c r="F81">
-        <v>0.1964463539589922</v>
+        <v>-1.146942742550453</v>
       </c>
       <c r="G81">
-        <v>-6.756069949618627</v>
+        <v>-6.619794303451696</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.348411291100506</v>
       </c>
       <c r="E82">
-        <v>-24.65947480250947</v>
+        <v>-24.0465480284026</v>
       </c>
       <c r="F82">
-        <v>-0.2936969815426697</v>
+        <v>-1.025053449432922</v>
       </c>
       <c r="G82">
-        <v>-6.669283577920839</v>
+        <v>-6.166263585317269</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.111430723578644</v>
       </c>
       <c r="E83">
-        <v>-27.80716043990643</v>
+        <v>-25.11953017417206</v>
       </c>
       <c r="F83">
-        <v>0.5403960967449861</v>
+        <v>-1.37032112475677</v>
       </c>
       <c r="G83">
-        <v>-7.403017680785681</v>
+        <v>-6.423153020849043</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.873505945604838</v>
       </c>
       <c r="E84">
-        <v>-26.27441364726713</v>
+        <v>-25.28574169139169</v>
       </c>
       <c r="F84">
-        <v>0.2083284559847483</v>
+        <v>-1.021525432664399</v>
       </c>
       <c r="G84">
-        <v>-7.443847115446102</v>
+        <v>-6.488828911783089</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.639669932122768</v>
       </c>
       <c r="E85">
-        <v>-29.46412563006002</v>
+        <v>-25.79115428393273</v>
       </c>
       <c r="F85">
-        <v>0.7433643345137266</v>
+        <v>-1.073551047397222</v>
       </c>
       <c r="G85">
-        <v>-7.217808848747514</v>
+        <v>-6.020409117245543</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.415165972552507</v>
       </c>
       <c r="E86">
-        <v>-29.33535738953938</v>
+        <v>-26.92324908648846</v>
       </c>
       <c r="F86">
-        <v>0.05816449830746234</v>
+        <v>-1.25424034386767</v>
       </c>
       <c r="G86">
-        <v>-6.791782324880466</v>
+        <v>-6.019667665781667</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.206177827430235</v>
       </c>
       <c r="E87">
-        <v>-30.45996810528777</v>
+        <v>-28.16635507454555</v>
       </c>
       <c r="F87">
-        <v>-0.5261758080361425</v>
+        <v>-1.403976035597709</v>
       </c>
       <c r="G87">
-        <v>-6.407600815319781</v>
+        <v>-5.716461010458953</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.014060350132571</v>
       </c>
       <c r="E88">
-        <v>-32.64835122069282</v>
+        <v>-29.12276696145538</v>
       </c>
       <c r="F88">
-        <v>-0.4320003747466723</v>
+        <v>-1.540215965601338</v>
       </c>
       <c r="G88">
-        <v>-6.693939449839314</v>
+        <v>-5.688236250684427</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.843991740478466</v>
       </c>
       <c r="E89">
-        <v>-32.41780853665725</v>
+        <v>-29.74680565246182</v>
       </c>
       <c r="F89">
-        <v>-0.1363452799112924</v>
+        <v>-1.639074988186236</v>
       </c>
       <c r="G89">
-        <v>-6.738739827022817</v>
+        <v>-5.401921112866215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.695213302348256</v>
       </c>
       <c r="E90">
-        <v>-34.43251266088061</v>
+        <v>-31.59517573973147</v>
       </c>
       <c r="F90">
-        <v>-0.339680484439473</v>
+        <v>-2.137397623423141</v>
       </c>
       <c r="G90">
-        <v>-5.356238304010914</v>
+        <v>-5.738325996409526</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.570837749066986</v>
       </c>
       <c r="E91">
-        <v>-35.19967309074632</v>
+        <v>-32.6761424342729</v>
       </c>
       <c r="F91">
-        <v>-0.5838956202958093</v>
+        <v>-1.821077246990121</v>
       </c>
       <c r="G91">
-        <v>-5.544512150199049</v>
+        <v>-5.220492638995979</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.471172914938972</v>
       </c>
       <c r="E92">
-        <v>-36.97854126310061</v>
+        <v>-34.26654202991781</v>
       </c>
       <c r="F92">
-        <v>-0.1013616677562637</v>
+        <v>-2.035246668779517</v>
       </c>
       <c r="G92">
-        <v>-6.299046055221291</v>
+        <v>-5.276866446951888</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.397019426580372</v>
       </c>
       <c r="E93">
-        <v>-35.89283160122622</v>
+        <v>-34.91111419771421</v>
       </c>
       <c r="F93">
-        <v>-1.200175288589155</v>
+        <v>-2.29837757427878</v>
       </c>
       <c r="G93">
-        <v>-5.787543753441194</v>
+        <v>-5.590740604673892</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.34963844218596</v>
       </c>
       <c r="E94">
-        <v>-40.01470071679194</v>
+        <v>-37.65035019076524</v>
       </c>
       <c r="F94">
-        <v>-0.6727976666990578</v>
+        <v>-2.184932658465387</v>
       </c>
       <c r="G94">
-        <v>-6.427442474212242</v>
+        <v>-5.742294328188018</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.327580786587289</v>
       </c>
       <c r="E95">
-        <v>-41.16814925537429</v>
+        <v>-39.31068363530327</v>
       </c>
       <c r="F95">
-        <v>-1.043424153324807</v>
+        <v>-2.47946697220478</v>
       </c>
       <c r="G95">
-        <v>-6.856121514583862</v>
+        <v>-5.890300049802821</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.332056904998507</v>
       </c>
       <c r="E96">
-        <v>-44.25967101602559</v>
+        <v>-39.64291354541594</v>
       </c>
       <c r="F96">
-        <v>-1.810826200380477</v>
+        <v>-2.595773069027441</v>
       </c>
       <c r="G96">
-        <v>-7.149028782494635</v>
+        <v>-6.447197978533197</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.357995334333774</v>
       </c>
       <c r="E97">
-        <v>-45.38800716233236</v>
+        <v>-42.46384320522635</v>
       </c>
       <c r="F97">
-        <v>-1.825722731385021</v>
+        <v>-2.656205784531276</v>
       </c>
       <c r="G97">
-        <v>-6.297570984527312</v>
+        <v>-6.519447724347666</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.404053633359187</v>
       </c>
       <c r="E98">
-        <v>-45.41542458689321</v>
+        <v>-43.6071641379931</v>
       </c>
       <c r="F98">
-        <v>-2.301272718351564</v>
+        <v>-2.944596925611508</v>
       </c>
       <c r="G98">
-        <v>-7.761227503153971</v>
+        <v>-7.168828669473638</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.459881135561616</v>
       </c>
       <c r="E99">
-        <v>-48.18597060181929</v>
+        <v>-45.49899239026291</v>
       </c>
       <c r="F99">
-        <v>-2.09662869332696</v>
+        <v>-2.911685060330881</v>
       </c>
       <c r="G99">
-        <v>-7.225831666876005</v>
+        <v>-6.975983409506464</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.520968292713779</v>
       </c>
       <c r="E100">
-        <v>-50.60507395104404</v>
+        <v>-47.98388987499277</v>
       </c>
       <c r="F100">
-        <v>-2.351518999903174</v>
+        <v>-3.018013471786822</v>
       </c>
       <c r="G100">
-        <v>-7.395143675098884</v>
+        <v>-7.231431714023943</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.569063222489958</v>
       </c>
       <c r="E101">
-        <v>-50.65529665898953</v>
+        <v>-48.98669313240093</v>
       </c>
       <c r="F101">
-        <v>-2.798553267395747</v>
+        <v>-3.222829797231208</v>
       </c>
       <c r="G101">
-        <v>-8.868700137215045</v>
+        <v>-7.818953676808077</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.60365828532993</v>
       </c>
       <c r="E102">
-        <v>-52.24273086174851</v>
+        <v>-51.46813722191419</v>
       </c>
       <c r="F102">
-        <v>-2.843402735318117</v>
+        <v>-3.365538448283299</v>
       </c>
       <c r="G102">
-        <v>-8.545179278228877</v>
+        <v>-7.79853504336098</v>
       </c>
     </row>
   </sheetData>
